--- a/event_registration_forms/035_golf_outing_registration_by_mickey_for_mickey--event_registration_forms.xlsx
+++ b/event_registration_forms/035_golf_outing_registration_by_mickey_for_mickey--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Team Size</t>
+          <t>Team Size (2)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members (2)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Team Member Names</t>
+          <t>Team Member Names (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Team Member Emails</t>
+          <t>Team Member Emails (2)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Team Member Phones</t>
+          <t>Team Member Phones (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>participant_notes</t>
+          <t>participant_notes_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Participant Notes</t>
+          <t>Participant Notes 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>participant_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Participant Name</t>
+          <t>Participant Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>participant_email</t>
+          <t>participant_email_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Participant Email</t>
+          <t>Participant Email 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
